--- a/data/trans_orig/IQ19B_M_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ19B_M_R-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,28</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15,58</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,74</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15,44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,77</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,12</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,94</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12,95</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5,6</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17,58</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16,38</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,29</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>6.275598809608169</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>15.57512087521331</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>17.73849445923177</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>15.43503006046289</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>4.773182449789011</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>19.12048686119142</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>14.93701912895289</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>12.94554248557677</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>5.603980866345172</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>17.57894197764501</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>16.37619468364347</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>14.2910935737564</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,71; 8,49</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12,29; 26,35</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14,85; 21,85</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12,73; 23,68</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,43; 6,62</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,06; 27,87</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,82; 20,24</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11,18; 14,76</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4,47; 7,0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14,4; 22,55</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14,56; 19,18</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>12,7; 18,66</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>4.710508144008577</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>12.29458963165606</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>14.85178885974924</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>12.73102915470638</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3.434740586417074</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>15.06446465703014</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>12.82365098495774</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>11.18386848587625</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>4.472113836436366</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>14.39918179478377</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>14.56333006962103</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>12.69719590406175</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.488742720557312</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>26.35476837701541</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>21.8539298579793</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>23.67893044864835</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6.620423321681601</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>27.87468626126311</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>20.23833129733797</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>14.76165279115986</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>7.003651388860727</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>22.55227456170668</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>19.18092746917126</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>18.66334727358213</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,13</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13,23</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,08</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>16,32</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,04</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13,89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,17</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17,26</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14,14</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,56</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3,98; 6,79</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>15,39; 22,92</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12,37; 14,4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13,86; 16,82</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,93; 6,95</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,25; 20,22</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,66; 16,92</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12,73; 15,59</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4,28; 6,37</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15,45; 20,43</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13,25; 15,36</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,64; 15,73</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>5.126813188780841</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>18.04764036247445</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>13.23457340156794</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>15.08064604106337</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>5.218761575710814</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>16.31560448045615</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>15.04066025603373</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>13.89013176999356</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.170317068205566</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>17.26111422989415</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>14.13985078967957</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>14.56152951447771</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,48</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>15,27</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16,6</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14,19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,71</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,49</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,7</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>14,69</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5,11</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>15,86</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>15,14</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>14,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>3.984475643014672</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>15.38779064077698</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>12.36876314729786</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>13.85512560260739</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>3.93264184011733</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>14.25171487657125</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>13.66037116667499</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>12.73044754935025</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>4.277733257094346</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>15.45212305994038</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>13.24580467494466</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>13.63941426581315</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4,22; 7,23</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>13,39; 18,5</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>14,03; 22,14</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12,29; 19,36</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>3,69; 6,03</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>13,94; 21,32</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>12,37; 16,95</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>13,17; 17,66</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>4,24; 6,06</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14,11; 18,52</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>13,58; 18,19</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>13,1; 17,0</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.793104474098755</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>22.9198863179159</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>14.40194267453146</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>16.82449922983875</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>6.945485950061959</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>20.21683640638102</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>16.92270173144004</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>15.58713279951469</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>6.367891127258178</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>20.42774117086213</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>15.36254692497845</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>15.7348745577419</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,47</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16,51</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14,38</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>19,23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,64</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,37</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,47</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19,68</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>17,3</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14,42</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,45</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.484251895529326</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>15.26955651611905</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>16.59673853721443</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>14.19412399797827</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>4.710189663276831</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>16.48948544162555</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>13.70407151023346</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>14.69211532286886</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5.106695328141249</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>15.86452985268413</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>15.14492553852693</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>14.42813496648741</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3,48; 6,47</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>14,05; 21,46</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12,76; 16,85</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15,1; 28,76</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,6; 6,1</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,34; 24,51</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,64; 17,16</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>14,99; 28,6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3,78; 5,69</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15,23; 21,42</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>13,26; 16,05</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>15,96; 26,35</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>4.221560464336718</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>13.38543211651908</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>14.03300942293759</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>12.29074726792333</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>3.688978007197662</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>13.93735625311746</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>12.36748257696613</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>13.17480828923373</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>4.240194345126254</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>14.11312082500815</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>13.58295144464397</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>13.09800169122522</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.230223425311369</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>18.50200487339458</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>22.14234898358876</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>19.35516676514477</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>6.025902217427028</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>21.3245785048167</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>16.94724471908836</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>17.65677897222712</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6.0625336339038</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>18.5244806733463</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>18.19304476130543</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>17.00275889385048</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>4.473217150866312</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>16.5056438512772</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>14.37641780864079</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>19.23355545808091</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>4.635907050287389</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>18.36628031852056</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>14.47084944642963</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>19.68317431729277</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>4.551517589979149</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>17.29712307859226</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>14.42009198724685</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>19.44546965068183</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>3.476320185308903</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>14.04745506984778</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>12.76466917406089</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>15.10206822799985</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>3.602046213181465</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>15.34392977548042</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>12.63660165620678</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>14.99158671322921</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>3.780625949353726</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>15.22879675820682</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>13.26473410787372</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>15.96268678922544</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.466291551287092</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>21.46048715653533</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>16.85114390619993</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>28.75904880629022</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>6.096130963343782</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>24.50855848595476</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>17.15855030627099</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>28.60467054221228</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5.692760576812436</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>21.42054722800606</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>16.04738665551582</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>26.35481453348065</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,25</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16,62</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,8</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,84</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,53</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,57</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15,16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5,06</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>17,05</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>14,87</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>15,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>4,6; 6,16</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15,14; 19,29</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14,16; 16,57</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14,5; 18,62</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,19; 5,55</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,74; 20,22</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,61; 15,99</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13,91; 17,37</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4,59; 5,64</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>15,72; 18,53</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14,14; 15,75</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,45; 16,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>5.249973449901451</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>16.62213626510309</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>15.16089878880592</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>15.79725990456561</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>4.840115162562335</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>17.52537706017931</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>14.56846267517851</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>15.16493001610354</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5.055947562968088</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>17.05268512691747</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>14.87322135569804</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>15.50885210886059</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>4.596931627998886</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>15.1437234049553</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>14.16443763935187</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>14.50345925567899</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>4.190196599461815</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>15.73778305865504</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>13.60681025171699</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>13.9102562724371</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>4.58709640348285</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>15.72072337637544</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>14.14032320797529</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>14.44710219567274</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.158440498945747</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>19.2930269677885</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>16.57261392492364</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>18.62238795250728</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>5.551690363258229</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>20.21717679961819</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>15.98785553990637</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>17.36835498816781</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>5.635146756189565</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>18.52972242268625</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>15.74783918042266</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>16.88593347316362</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
